--- a/01_pyRevitAPI/addins_KSC01/KSC01_FVC_GE_DO_GE_SharedParameters.xlsx
+++ b/01_pyRevitAPI/addins_KSC01/KSC01_FVC_GE_DO_GE_SharedParameters.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ca6199192a2acbc2/Desktop/RevitAPI/01_pyRevitAPI/addins_KSC01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="129" documentId="13_ncr:1_{5520F43F-CA34-45F4-8048-FF315C1B2109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79211DFE-6937-4743-916D-AB3D6C6C470D}"/>
+  <xr:revisionPtr revIDLastSave="239" documentId="13_ncr:1_{5520F43F-CA34-45F4-8048-FF315C1B2109}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5FACF98-0ACD-4D0A-94D9-9EFD99A75926}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SharedParameter" sheetId="2" r:id="rId1"/>
     <sheet name="260406_1F_UpdateBy室名" sheetId="5" r:id="rId2"/>
     <sheet name="260409_1F_UpdateBy室名 " sheetId="6" r:id="rId3"/>
+    <sheet name="260409_2F_UpdateBy室名  " sheetId="7" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="ElementID">#REF!</definedName>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -63,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="113">
   <si>
     <t>Shared Parameters Name</t>
   </si>
@@ -336,6 +337,72 @@
   </si>
   <si>
     <t>調理・配送従事者用トイレ2</t>
+  </si>
+  <si>
+    <t>事業者用事務室</t>
+  </si>
+  <si>
+    <t>事業者用会議室</t>
+  </si>
+  <si>
+    <t>食堂兼休憩室</t>
+  </si>
+  <si>
+    <t>洗濯・乾燥室</t>
+  </si>
+  <si>
+    <t>物品庫3</t>
+  </si>
+  <si>
+    <t>事業者用廊下</t>
+  </si>
+  <si>
+    <t>2FL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">物入1 </t>
+  </si>
+  <si>
+    <t>物入2</t>
+  </si>
+  <si>
+    <t>調理員更衣室（男）</t>
+  </si>
+  <si>
+    <t>調理員更衣室（女）</t>
+  </si>
+  <si>
+    <t>会議室</t>
+  </si>
+  <si>
+    <t>倉庫2</t>
+  </si>
+  <si>
+    <t>倉庫3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">小会議室 </t>
+  </si>
+  <si>
+    <t>試作調理室</t>
+  </si>
+  <si>
+    <t>廊下 見学者通路 展示コーナー</t>
+  </si>
+  <si>
+    <t>外来用トイレ（男）</t>
+  </si>
+  <si>
+    <t>外来用トイレ（女）</t>
+  </si>
+  <si>
+    <t>外来用トイレ(多目的)</t>
+  </si>
+  <si>
+    <t>市職員用事務室1</t>
+  </si>
+  <si>
+    <t>市職員用事務室2</t>
   </si>
 </sst>
 </file>
@@ -417,14 +484,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -441,6 +507,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1848,7 +1918,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36F8B2EA-6BF5-4E37-B931-539A8AA4803B}">
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="44.77734375" customWidth="1"/>
@@ -1882,10 +1952,10 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C2">
-        <v>2500</v>
+        <v>2180</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -1896,13 +1966,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>111</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>2700</v>
+        <v>2330</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>
@@ -1913,10 +1983,1097 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>2060</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>11</v>
       </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>2400</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>2400</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>2700</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>2700</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9">
+        <v>7000</v>
+      </c>
+      <c r="D9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>3200</v>
+      </c>
+      <c r="D10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11">
+        <v>3300</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <v>2700</v>
+      </c>
+      <c r="D12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>3200</v>
+      </c>
+      <c r="D13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14">
+        <v>3200</v>
+      </c>
+      <c r="D14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15">
+        <v>3200</v>
+      </c>
+      <c r="D15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16">
+        <v>3200</v>
+      </c>
+      <c r="D16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17">
+        <v>3200</v>
+      </c>
+      <c r="D17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18">
+        <v>2700</v>
+      </c>
+      <c r="D18" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19">
+        <v>2700</v>
+      </c>
+      <c r="D19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20">
+        <v>2700</v>
+      </c>
+      <c r="D20" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21">
+        <v>2700</v>
+      </c>
+      <c r="D21" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22">
+        <v>2700</v>
+      </c>
+      <c r="D22" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23">
+        <v>2700</v>
+      </c>
+      <c r="D23" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24">
+        <v>2700</v>
+      </c>
+      <c r="D24" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25">
+        <v>2700</v>
+      </c>
+      <c r="D25" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26">
+        <v>2700</v>
+      </c>
+      <c r="D26" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27">
+        <v>1610</v>
+      </c>
+      <c r="D27" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28">
+        <v>2700</v>
+      </c>
+      <c r="D28" t="s">
+        <v>6</v>
+      </c>
+      <c r="E28" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29">
+        <v>2700</v>
+      </c>
+      <c r="D29" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30">
+        <v>3200</v>
+      </c>
+      <c r="D30" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>50</v>
+      </c>
+      <c r="B31" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31">
+        <v>2080</v>
+      </c>
+      <c r="D31" t="s">
+        <v>6</v>
+      </c>
+      <c r="E31" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32">
+        <v>2380</v>
+      </c>
+      <c r="D32" t="s">
+        <v>6</v>
+      </c>
+      <c r="E32" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33">
+        <v>2400</v>
+      </c>
+      <c r="D33" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34">
+        <v>2300</v>
+      </c>
+      <c r="D34" t="s">
+        <v>6</v>
+      </c>
+      <c r="E34" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35">
+        <v>2400</v>
+      </c>
+      <c r="D35" t="s">
+        <v>6</v>
+      </c>
+      <c r="E35" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>58</v>
+      </c>
+      <c r="B36" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36">
+        <v>2700</v>
+      </c>
+      <c r="D36" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37">
+        <v>2300</v>
+      </c>
+      <c r="D37" t="s">
+        <v>6</v>
+      </c>
+      <c r="E37" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39">
+        <v>2500</v>
+      </c>
+      <c r="D39" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>63</v>
+      </c>
+      <c r="B40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40">
+        <v>2700</v>
+      </c>
+      <c r="D40" t="s">
+        <v>6</v>
+      </c>
+      <c r="E40" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>85</v>
+      </c>
+      <c r="B41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41">
+        <v>2700</v>
+      </c>
+      <c r="D41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E41" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42">
+        <v>2700</v>
+      </c>
+      <c r="D42" t="s">
+        <v>6</v>
+      </c>
+      <c r="E42" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>64</v>
+      </c>
+      <c r="B43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43">
+        <v>2700</v>
+      </c>
+      <c r="D43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>65</v>
+      </c>
+      <c r="B44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44">
+        <v>3200</v>
+      </c>
+      <c r="D44" t="s">
+        <v>6</v>
+      </c>
+      <c r="E44" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>66</v>
+      </c>
+      <c r="B45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45">
+        <v>2700</v>
+      </c>
+      <c r="D45" t="s">
+        <v>6</v>
+      </c>
+      <c r="E45" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>67</v>
+      </c>
+      <c r="B46" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46">
+        <v>4500</v>
+      </c>
+      <c r="D46" t="s">
+        <v>6</v>
+      </c>
+      <c r="E46" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>68</v>
+      </c>
+      <c r="B47" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47">
+        <v>4500</v>
+      </c>
+      <c r="D47" t="s">
+        <v>6</v>
+      </c>
+      <c r="E47" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>69</v>
+      </c>
+      <c r="B48" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48">
+        <v>2700</v>
+      </c>
+      <c r="D48" t="s">
+        <v>6</v>
+      </c>
+      <c r="E48" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>71</v>
+      </c>
+      <c r="B49" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49">
+        <v>2700</v>
+      </c>
+      <c r="D49" t="s">
+        <v>6</v>
+      </c>
+      <c r="E49" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>72</v>
+      </c>
+      <c r="B50" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50">
+        <v>2700</v>
+      </c>
+      <c r="D50" t="s">
+        <v>6</v>
+      </c>
+      <c r="E50" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>73</v>
+      </c>
+      <c r="B51" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51">
+        <v>2050</v>
+      </c>
+      <c r="D51" t="s">
+        <v>6</v>
+      </c>
+      <c r="E51" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>75</v>
+      </c>
+      <c r="B53" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53">
+        <v>2400</v>
+      </c>
+      <c r="D53" t="s">
+        <v>6</v>
+      </c>
+      <c r="E53" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>76</v>
+      </c>
+      <c r="B54" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54">
+        <v>2700</v>
+      </c>
+      <c r="D54" t="s">
+        <v>6</v>
+      </c>
+      <c r="E54" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>77</v>
+      </c>
+      <c r="B55" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55">
+        <v>2700</v>
+      </c>
+      <c r="D55" t="s">
+        <v>6</v>
+      </c>
+      <c r="E55" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>78</v>
+      </c>
+      <c r="B56" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56">
+        <v>2700</v>
+      </c>
+      <c r="D56" t="s">
+        <v>6</v>
+      </c>
+      <c r="E56" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>79</v>
+      </c>
+      <c r="B57" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57">
+        <v>1400</v>
+      </c>
+      <c r="D57" t="s">
+        <v>6</v>
+      </c>
+      <c r="E57" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>89</v>
+      </c>
+      <c r="B58" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58">
+        <v>2300</v>
+      </c>
+      <c r="D58" t="s">
+        <v>6</v>
+      </c>
+      <c r="E58" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>90</v>
+      </c>
+      <c r="B59" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59">
+        <v>2300</v>
+      </c>
+      <c r="D59" t="s">
+        <v>6</v>
+      </c>
+      <c r="E59" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>80</v>
+      </c>
+      <c r="B60" t="s">
+        <v>12</v>
+      </c>
+      <c r="C60">
+        <v>2050</v>
+      </c>
+      <c r="D60" t="s">
+        <v>6</v>
+      </c>
+      <c r="E60" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>81</v>
+      </c>
+      <c r="B61" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61">
+        <v>2050</v>
+      </c>
+      <c r="D61" t="s">
+        <v>6</v>
+      </c>
+      <c r="E61" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>82</v>
+      </c>
+      <c r="B62" t="s">
+        <v>12</v>
+      </c>
+      <c r="C62">
+        <v>2700</v>
+      </c>
+      <c r="D62" t="s">
+        <v>6</v>
+      </c>
+      <c r="E62" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>84</v>
+      </c>
+      <c r="B63" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63">
+        <v>1510</v>
+      </c>
+      <c r="D63" t="s">
+        <v>6</v>
+      </c>
+      <c r="E63" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="86" ht="13.8" customHeight="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D144E7CF-F3AC-49C9-8A60-F6099C0F2591}">
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="44.77734375" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" customWidth="1"/>
+    <col min="3" max="3" width="31.21875" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" customWidth="1"/>
+    <col min="5" max="5" width="46.88671875" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="str" cm="1">
+        <f t="array" ref="A1:E1">TRANSPOSE(_xlfn._xlws.FILTER(SharedParameter!A2:A1000,SharedParameter!A2:A1000&lt;&gt;"",""))</f>
+        <v>01_室名</v>
+      </c>
+      <c r="B1" s="5" t="str">
+        <v>02_フロアレベル</v>
+      </c>
+      <c r="C1" s="5" t="str">
+        <v>03_天井レベル</v>
+      </c>
+      <c r="D1" s="5" t="str">
+        <v>04_参考図受領日</v>
+      </c>
+      <c r="E1" s="5" t="str">
+        <v>05_フロアレベル参考ページ</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2">
+        <v>2400</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3">
+        <v>2400</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>93</v>
+      </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="C4">
         <v>2400</v>
@@ -1925,15 +3082,15 @@
         <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="C5">
         <v>2400</v>
@@ -1942,270 +3099,270 @@
         <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="C6">
-        <v>2700</v>
+        <v>2400</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="C7">
-        <v>2700</v>
+        <v>2300</v>
       </c>
       <c r="D7" t="s">
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>99</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="C8">
-        <v>7000</v>
+        <v>2300</v>
       </c>
       <c r="D8" t="s">
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="C9">
-        <v>3200</v>
+        <v>2400</v>
       </c>
       <c r="D9" t="s">
         <v>6</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="C10">
-        <v>3300</v>
+        <v>2500</v>
       </c>
       <c r="D10" t="s">
         <v>6</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="C11">
-        <v>2700</v>
+        <v>2400</v>
       </c>
       <c r="D11" t="s">
         <v>6</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="C12">
-        <v>3200</v>
+        <v>2300</v>
       </c>
       <c r="D12" t="s">
         <v>6</v>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="C13">
-        <v>3200</v>
+        <v>2300</v>
       </c>
       <c r="D13" t="s">
         <v>6</v>
       </c>
       <c r="E13" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="C14">
-        <v>3200</v>
+        <v>2300</v>
       </c>
       <c r="D14" t="s">
         <v>6</v>
       </c>
       <c r="E14" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="C15">
-        <v>3200</v>
+        <v>2300</v>
       </c>
       <c r="D15" t="s">
         <v>6</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>102</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="C16">
-        <v>3200</v>
+        <v>2700</v>
       </c>
       <c r="D16" t="s">
         <v>6</v>
       </c>
       <c r="E16" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="C17">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="D17" t="s">
         <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="C18">
-        <v>2700</v>
+        <v>2400</v>
       </c>
       <c r="D18" t="s">
         <v>6</v>
       </c>
       <c r="E18" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>105</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="C19">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="D19" t="s">
         <v>6</v>
       </c>
       <c r="E19" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>106</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="C20">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="D20" t="s">
         <v>6</v>
       </c>
       <c r="E20" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="C21">
         <v>2700</v>
@@ -2214,697 +3371,57 @@
         <v>6</v>
       </c>
       <c r="E21" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="C22">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="D22" t="s">
         <v>6</v>
       </c>
       <c r="E22" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="C23">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="D23" t="s">
         <v>6</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="C24">
-        <v>2700</v>
+        <v>2500</v>
       </c>
       <c r="D24" t="s">
         <v>6</v>
       </c>
       <c r="E24" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25">
-        <v>2700</v>
-      </c>
-      <c r="D25" t="s">
-        <v>6</v>
-      </c>
-      <c r="E25" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>44</v>
-      </c>
-      <c r="B26" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26">
-        <v>1610</v>
-      </c>
-      <c r="D26" t="s">
-        <v>6</v>
-      </c>
-      <c r="E26" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27">
-        <v>2700</v>
-      </c>
-      <c r="D27" t="s">
-        <v>6</v>
-      </c>
-      <c r="E27" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28">
-        <v>2700</v>
-      </c>
-      <c r="D28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E28" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>49</v>
-      </c>
-      <c r="B29" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29">
-        <v>3200</v>
-      </c>
-      <c r="D29" t="s">
-        <v>6</v>
-      </c>
-      <c r="E29" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>50</v>
-      </c>
-      <c r="B30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30">
-        <v>2400</v>
-      </c>
-      <c r="D30" t="s">
-        <v>6</v>
-      </c>
-      <c r="E30" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>52</v>
-      </c>
-      <c r="B31" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31">
-        <v>2700</v>
-      </c>
-      <c r="D31" t="s">
-        <v>6</v>
-      </c>
-      <c r="E31" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>53</v>
-      </c>
-      <c r="B32" t="s">
-        <v>12</v>
-      </c>
-      <c r="C32">
-        <v>2400</v>
-      </c>
-      <c r="D32" t="s">
-        <v>6</v>
-      </c>
-      <c r="E32" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>55</v>
-      </c>
-      <c r="B33" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33">
-        <v>2300</v>
-      </c>
-      <c r="D33" t="s">
-        <v>6</v>
-      </c>
-      <c r="E33" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>57</v>
-      </c>
-      <c r="B34" t="s">
-        <v>12</v>
-      </c>
-      <c r="C34">
-        <v>2400</v>
-      </c>
-      <c r="D34" t="s">
-        <v>6</v>
-      </c>
-      <c r="E34" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" s="6">
-        <v>2700</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" s="6">
-        <v>2300</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C38" s="6">
-        <v>2500</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C39" s="6">
-        <v>2700</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" s="6">
-        <v>2700</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C41" s="6">
-        <v>2700</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" s="6">
-        <v>2700</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C43" s="6">
-        <v>3200</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C44" s="6">
-        <v>2700</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C45" s="6">
-        <v>4500</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C46" s="6">
-        <v>4500</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C47" s="6">
-        <v>2700</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" s="6">
-        <v>2700</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C49" s="6">
-        <v>2700</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C50" s="6">
-        <v>2050</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C52" s="6">
-        <v>2400</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C53" s="6">
-        <v>2700</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C54" s="6">
-        <v>2700</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C55" s="6">
-        <v>2700</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C56" s="6">
-        <v>1400</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C57" s="6">
-        <v>2300</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C58" s="6">
-        <v>2300</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C59" s="6">
-        <v>2050</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C60" s="6">
-        <v>2050</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C61" s="6">
-        <v>2700</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C62" s="6">
-        <v>1510</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E62" s="6" t="s">
         <v>86</v>
       </c>
     </row>
